--- a/prix/v33.xlsx
+++ b/prix/v33.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{812F6640-D9E6-4317-ABD6-A3BEF7BFCDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20ECE597-A12A-4DB2-8236-E13AFF0FA1F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="232">
   <si>
     <t>path</t>
   </si>
@@ -723,6 +723,15 @@
   </si>
   <si>
     <t>v33/vitrificateur-parquet.png</t>
+  </si>
+  <si>
+    <t>3109518710</t>
+  </si>
+  <si>
+    <t>V33 protection invisible  0.75t</t>
+  </si>
+  <si>
+    <t>0,75l Invisible</t>
   </si>
 </sst>
 </file>
@@ -787,7 +796,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -836,6 +845,10 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1184,7 +1197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065E4AF0-A4F8-4CE3-9E23-EDCEACB756BD}">
-  <dimension ref="A1:G444"/>
+  <dimension ref="A1:G445"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.88671875" style="4" bestFit="1" customWidth="1"/>
@@ -1227,16 +1240,16 @@
       <c r="C2" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="20">
         <v>21.150000000000002</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="21">
         <v>3</v>
       </c>
-      <c r="G2" s="9"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
@@ -1248,16 +1261,16 @@
       <c r="C3" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="20">
         <v>35</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="21">
         <v>2</v>
       </c>
-      <c r="G3" s="9"/>
+      <c r="G3" s="19"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
@@ -1269,16 +1282,16 @@
       <c r="C4" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="20">
         <v>14.8</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="21">
         <v>2</v>
       </c>
-      <c r="G4" s="9"/>
+      <c r="G4" s="19"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
@@ -1290,16 +1303,16 @@
       <c r="C5" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>21.55</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="21">
         <v>2</v>
       </c>
-      <c r="G5" s="9"/>
+      <c r="G5" s="19"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
@@ -1311,16 +1324,16 @@
       <c r="C6" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="20">
         <v>35</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="19">
-        <v>3</v>
-      </c>
-      <c r="G6" s="9"/>
+      <c r="F6" s="21">
+        <v>2</v>
+      </c>
+      <c r="G6" s="19"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
@@ -1332,16 +1345,16 @@
       <c r="C7" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="20">
         <v>15.1</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="F7" s="19">
-        <v>1</v>
-      </c>
-      <c r="G7" s="9"/>
+      <c r="F7" s="21">
+        <v>0</v>
+      </c>
+      <c r="G7" s="19"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
@@ -1353,16 +1366,16 @@
       <c r="C8" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="20">
         <v>21.55</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="21">
         <v>5</v>
       </c>
-      <c r="G8" s="9"/>
+      <c r="G8" s="19"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
@@ -1374,16 +1387,16 @@
       <c r="C9" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="D9" s="18">
-        <v>35.590000000000003</v>
+      <c r="D9" s="20">
+        <v>37.35</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="19">
-        <v>2</v>
-      </c>
-      <c r="G9" s="9"/>
+      <c r="F9" s="21">
+        <v>3</v>
+      </c>
+      <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
@@ -1395,16 +1408,16 @@
       <c r="C10" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="20">
         <v>29.25</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="19">
-        <v>2</v>
-      </c>
-      <c r="G10" s="9"/>
+      <c r="F10" s="21">
+        <v>1</v>
+      </c>
+      <c r="G10" s="19"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
@@ -1416,16 +1429,16 @@
       <c r="C11" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="20">
         <v>16.71</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="21">
         <v>2</v>
       </c>
-      <c r="G11" s="9"/>
+      <c r="G11" s="19"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
@@ -1437,16 +1450,16 @@
       <c r="C12" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="20">
         <v>15.290000000000001</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="21">
         <v>3</v>
       </c>
-      <c r="G12" s="9"/>
+      <c r="G12" s="19"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
@@ -1458,16 +1471,16 @@
       <c r="C13" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="18">
-        <v>15.1</v>
+      <c r="D13" s="20">
+        <v>15.85</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="F13" s="19">
-        <v>0</v>
-      </c>
-      <c r="G13" s="9"/>
+      <c r="F13" s="21">
+        <v>3</v>
+      </c>
+      <c r="G13" s="19"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
@@ -1479,16 +1492,16 @@
       <c r="C14" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="20">
         <v>13.65</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="21">
         <v>1</v>
       </c>
-      <c r="G14" s="9"/>
+      <c r="G14" s="19"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
@@ -1500,16 +1513,16 @@
       <c r="C15" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="20">
         <v>13.65</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="21">
         <v>2</v>
       </c>
-      <c r="G15" s="9"/>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
@@ -1521,16 +1534,16 @@
       <c r="C16" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="20">
         <v>12.950000000000001</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="21">
         <v>1</v>
       </c>
-      <c r="G16" s="9"/>
+      <c r="G16" s="19"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
@@ -1542,16 +1555,16 @@
       <c r="C17" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="20">
         <v>15.08</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="21">
         <v>4</v>
       </c>
-      <c r="G17" s="9"/>
+      <c r="G17" s="19"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
@@ -1563,16 +1576,16 @@
       <c r="C18" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="20">
         <v>15.290000000000001</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="21">
         <v>2</v>
       </c>
-      <c r="G18" s="9"/>
+      <c r="G18" s="19"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
@@ -1584,16 +1597,16 @@
       <c r="C19" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="20">
         <v>34.99</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="21">
         <v>1</v>
       </c>
-      <c r="G19" s="9"/>
+      <c r="G19" s="19"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
@@ -1605,16 +1618,16 @@
       <c r="C20" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="20">
         <v>40.97</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="21">
         <v>6</v>
       </c>
-      <c r="G20" s="9"/>
+      <c r="G20" s="19"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
@@ -1626,16 +1639,16 @@
       <c r="C21" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="20">
         <v>32.75</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="21">
         <v>3</v>
       </c>
-      <c r="G21" s="9"/>
+      <c r="G21" s="19"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
@@ -1647,16 +1660,16 @@
       <c r="C22" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="20">
         <v>29.95</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="21">
         <v>2</v>
       </c>
-      <c r="G22" s="9"/>
+      <c r="G22" s="19"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
@@ -1668,16 +1681,16 @@
       <c r="C23" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="20">
         <v>41.68</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="21">
         <v>2</v>
       </c>
-      <c r="G23" s="9"/>
+      <c r="G23" s="19"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
@@ -1689,16 +1702,16 @@
       <c r="C24" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="D24" s="18">
+      <c r="D24" s="20">
         <v>37.65</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="21">
         <v>1</v>
       </c>
-      <c r="G24" s="9"/>
+      <c r="G24" s="19"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
@@ -1710,16 +1723,16 @@
       <c r="C25" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="D25" s="18">
+      <c r="D25" s="20">
         <v>29.95</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="21">
         <v>3</v>
       </c>
-      <c r="G25" s="9"/>
+      <c r="G25" s="19"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
@@ -1731,16 +1744,16 @@
       <c r="C26" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="D26" s="18">
+      <c r="D26" s="20">
         <v>33.75</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="21">
         <v>1</v>
       </c>
-      <c r="G26" s="9"/>
+      <c r="G26" s="19"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
@@ -1752,16 +1765,16 @@
       <c r="C27" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="20">
         <v>37.86</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="21">
         <v>2</v>
       </c>
-      <c r="G27" s="9"/>
+      <c r="G27" s="19"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
@@ -1773,16 +1786,16 @@
       <c r="C28" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="D28" s="18">
+      <c r="D28" s="20">
         <v>37.32</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="21">
         <v>5</v>
       </c>
-      <c r="G28" s="9"/>
+      <c r="G28" s="19"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
@@ -1794,16 +1807,16 @@
       <c r="C29" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="D29" s="18">
+      <c r="D29" s="20">
         <v>29.990000000000002</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F29" s="21">
         <v>2</v>
       </c>
-      <c r="G29" s="9"/>
+      <c r="G29" s="19"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
@@ -1815,16 +1828,16 @@
       <c r="C30" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="D30" s="18">
+      <c r="D30" s="20">
         <v>29.990000000000002</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="F30" s="19">
+      <c r="F30" s="21">
         <v>1</v>
       </c>
-      <c r="G30" s="9"/>
+      <c r="G30" s="19"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
@@ -1836,16 +1849,16 @@
       <c r="C31" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="D31" s="18">
+      <c r="D31" s="20">
         <v>30.85</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="21">
         <v>3</v>
       </c>
-      <c r="G31" s="9"/>
+      <c r="G31" s="19"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
@@ -1857,16 +1870,16 @@
       <c r="C32" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="D32" s="18">
+      <c r="D32" s="20">
         <v>64.3</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="F32" s="19">
+      <c r="F32" s="21">
         <v>2</v>
       </c>
-      <c r="G32" s="9"/>
+      <c r="G32" s="19"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
@@ -1878,16 +1891,16 @@
       <c r="C33" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="D33" s="18">
+      <c r="D33" s="20">
         <v>115.10000000000001</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="F33" s="19">
+      <c r="F33" s="21">
         <v>2</v>
       </c>
-      <c r="G33" s="9"/>
+      <c r="G33" s="19"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
@@ -1899,16 +1912,16 @@
       <c r="C34" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="D34" s="18">
+      <c r="D34" s="20">
         <v>113.10000000000001</v>
       </c>
       <c r="E34" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="F34" s="19">
+      <c r="F34" s="21">
         <v>2</v>
       </c>
-      <c r="G34" s="9"/>
+      <c r="G34" s="19"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
@@ -1920,16 +1933,16 @@
       <c r="C35" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="D35" s="18">
+      <c r="D35" s="20">
         <v>75</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="F35" s="19">
+      <c r="F35" s="21">
         <v>1</v>
       </c>
-      <c r="G35" s="9"/>
+      <c r="G35" s="19"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
@@ -1941,16 +1954,16 @@
       <c r="C36" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="D36" s="18">
-        <v>91.52</v>
+      <c r="D36" s="20">
+        <v>95.7</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="F36" s="19">
-        <v>2</v>
-      </c>
-      <c r="G36" s="9"/>
+      <c r="F36" s="21">
+        <v>1</v>
+      </c>
+      <c r="G36" s="19"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
@@ -1962,661 +1975,660 @@
       <c r="C37" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="D37" s="18">
-        <v>42.5</v>
+      <c r="D37" s="20">
+        <v>42.25</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="F37" s="19">
-        <v>5</v>
-      </c>
-      <c r="G37" s="9"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F37" s="21">
+        <v>2</v>
+      </c>
+      <c r="G37" s="19"/>
+    </row>
+    <row r="38" spans="1:7" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>42</v>
+        <v>230</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="D38" s="18">
-        <v>74.95</v>
+        <v>231</v>
+      </c>
+      <c r="D38" s="20">
+        <v>38.300000000000004</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="F38" s="19">
-        <v>1</v>
-      </c>
-      <c r="G38" s="9"/>
+        <v>229</v>
+      </c>
+      <c r="F38" s="21">
+        <v>6</v>
+      </c>
+      <c r="G38" s="19"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>219</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="D39" s="18">
+        <v>195</v>
+      </c>
+      <c r="D39" s="20">
         <v>74.95</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="F39" s="19">
+        <v>115</v>
+      </c>
+      <c r="F39" s="21">
         <v>1</v>
       </c>
-      <c r="G39" s="9"/>
+      <c r="G39" s="19"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
         <v>219</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D40" s="18">
+        <v>196</v>
+      </c>
+      <c r="D40" s="20">
         <v>74.95</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="F40" s="19">
+        <v>116</v>
+      </c>
+      <c r="F40" s="21">
         <v>1</v>
       </c>
-      <c r="G40" s="9"/>
+      <c r="G40" s="19"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
         <v>219</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="D41" s="18">
-        <v>90.2</v>
+        <v>197</v>
+      </c>
+      <c r="D41" s="20">
+        <v>74.95</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F41" s="19">
-        <v>3</v>
-      </c>
-      <c r="G41" s="9"/>
+        <v>117</v>
+      </c>
+      <c r="F41" s="21">
+        <v>1</v>
+      </c>
+      <c r="G41" s="19"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
         <v>219</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="D42" s="18">
+        <v>198</v>
+      </c>
+      <c r="D42" s="20">
         <v>90.2</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="F42" s="19">
-        <v>1</v>
-      </c>
-      <c r="G42" s="9"/>
+        <v>118</v>
+      </c>
+      <c r="F42" s="21">
+        <v>3</v>
+      </c>
+      <c r="G42" s="19"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="D43" s="18">
-        <v>77.989999999999995</v>
+        <v>199</v>
+      </c>
+      <c r="D43" s="20">
+        <v>90.2</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="F43" s="19">
+        <v>119</v>
+      </c>
+      <c r="F43" s="21">
         <v>1</v>
       </c>
-      <c r="G43" s="9"/>
+      <c r="G43" s="19"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
         <v>228</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="D44" s="18">
+        <v>198</v>
+      </c>
+      <c r="D44" s="20">
         <v>77.989999999999995</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F44" s="19">
-        <v>2</v>
-      </c>
-      <c r="G44" s="9"/>
+        <v>120</v>
+      </c>
+      <c r="F44" s="21">
+        <v>1</v>
+      </c>
+      <c r="G44" s="19"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>228</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="D45" s="18">
+        <v>200</v>
+      </c>
+      <c r="D45" s="20">
         <v>77.989999999999995</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="F45" s="19">
-        <v>3</v>
-      </c>
-      <c r="G45" s="9"/>
+        <v>121</v>
+      </c>
+      <c r="F45" s="21">
+        <v>2</v>
+      </c>
+      <c r="G45" s="19"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" s="20">
+        <v>77.989999999999995</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F46" s="21">
+        <v>3</v>
+      </c>
+      <c r="G46" s="19"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B47" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C47" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="D46" s="18">
+      <c r="D47" s="20">
         <v>75</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E47" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="F46" s="19">
+      <c r="F47" s="21">
         <v>3</v>
       </c>
-      <c r="G46" s="9"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="10"/>
-      <c r="B47" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="D47" s="18">
-        <v>19.72</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F47" s="19">
-        <v>4</v>
-      </c>
-      <c r="G47" s="9"/>
+      <c r="G47" s="19"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="10"/>
       <c r="B48" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D48" s="20">
+        <v>19.72</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F48" s="21">
+        <v>2</v>
+      </c>
+      <c r="G48" s="19"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="10"/>
+      <c r="B49" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C49" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="D48" s="18">
+      <c r="D49" s="20">
         <v>63.2</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E49" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F48" s="19">
+      <c r="F49" s="21">
         <v>0</v>
       </c>
-      <c r="G48" s="9"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="D49" s="18">
-        <v>36.54</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="F49" s="19">
-        <v>3</v>
-      </c>
-      <c r="G49" s="9"/>
+      <c r="G49" s="19"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="10" t="s">
         <v>217</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="D50" s="18">
+        <v>202</v>
+      </c>
+      <c r="D50" s="20">
         <v>36.54</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="F50" s="19">
-        <v>0</v>
-      </c>
-      <c r="G50" s="9"/>
+        <v>126</v>
+      </c>
+      <c r="F50" s="21">
+        <v>2</v>
+      </c>
+      <c r="G50" s="19"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>217</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="D51" s="18">
-        <v>36.57</v>
+        <v>203</v>
+      </c>
+      <c r="D51" s="20">
+        <v>36.54</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="F51" s="19">
-        <v>1</v>
-      </c>
-      <c r="G51" s="9"/>
+        <v>127</v>
+      </c>
+      <c r="F51" s="21">
+        <v>0</v>
+      </c>
+      <c r="G51" s="19"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="10" t="s">
         <v>217</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="D52" s="18">
-        <v>63.15</v>
+        <v>55</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D52" s="20">
+        <v>36.57</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="F52" s="19">
-        <v>3</v>
-      </c>
-      <c r="G52" s="9"/>
+        <v>128</v>
+      </c>
+      <c r="F52" s="21">
+        <v>1</v>
+      </c>
+      <c r="G52" s="19"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>217</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="D53" s="18">
+        <v>205</v>
+      </c>
+      <c r="D53" s="20">
         <v>63.15</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="F53" s="19">
-        <v>3</v>
-      </c>
-      <c r="G53" s="9"/>
+        <v>129</v>
+      </c>
+      <c r="F53" s="21">
+        <v>2</v>
+      </c>
+      <c r="G53" s="19"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="10" t="s">
         <v>217</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="D54" s="18">
+        <v>206</v>
+      </c>
+      <c r="D54" s="20">
         <v>63.15</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="F54" s="19">
-        <v>2</v>
-      </c>
-      <c r="G54" s="9"/>
+        <v>130</v>
+      </c>
+      <c r="F54" s="21">
+        <v>1</v>
+      </c>
+      <c r="G54" s="19"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="D55" s="18">
-        <v>41.56</v>
+        <v>58</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D55" s="20">
+        <v>63.15</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="F55" s="19">
+        <v>131</v>
+      </c>
+      <c r="F55" s="21">
         <v>1</v>
       </c>
-      <c r="G55" s="9"/>
+      <c r="G55" s="19"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="10" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>209</v>
-      </c>
-      <c r="D56" s="18">
-        <v>21.55</v>
+        <v>208</v>
+      </c>
+      <c r="D56" s="20">
+        <v>41.56</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="F56" s="19">
-        <v>3</v>
-      </c>
-      <c r="G56" s="9"/>
+        <v>132</v>
+      </c>
+      <c r="F56" s="21">
+        <v>1</v>
+      </c>
+      <c r="G56" s="19"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="10" t="s">
         <v>225</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="D57" s="18">
+        <v>209</v>
+      </c>
+      <c r="D57" s="20">
         <v>21.55</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="F57" s="19">
-        <v>3</v>
-      </c>
-      <c r="G57" s="9"/>
+        <v>133</v>
+      </c>
+      <c r="F57" s="21">
+        <v>2</v>
+      </c>
+      <c r="G57" s="19"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
         <v>225</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="D58" s="18">
-        <v>21.150000000000002</v>
+        <v>210</v>
+      </c>
+      <c r="D58" s="20">
+        <v>21.55</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="F58" s="19">
-        <v>2</v>
-      </c>
-      <c r="G58" s="9"/>
+        <v>134</v>
+      </c>
+      <c r="F58" s="21">
+        <v>3</v>
+      </c>
+      <c r="G58" s="19"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="10" t="s">
         <v>225</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="D59" s="18">
+        <v>211</v>
+      </c>
+      <c r="D59" s="20">
         <v>21.150000000000002</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="F59" s="19">
-        <v>4</v>
-      </c>
-      <c r="G59" s="9"/>
+        <v>135</v>
+      </c>
+      <c r="F59" s="21">
+        <v>2</v>
+      </c>
+      <c r="G59" s="19"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="10" t="s">
         <v>225</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="D60" s="18">
+        <v>212</v>
+      </c>
+      <c r="D60" s="20">
         <v>21.150000000000002</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="F60" s="19">
-        <v>2</v>
-      </c>
-      <c r="G60" s="9"/>
+        <v>136</v>
+      </c>
+      <c r="F60" s="21">
+        <v>4</v>
+      </c>
+      <c r="G60" s="19"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="10" t="s">
         <v>225</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="D61" s="18">
-        <v>21.55</v>
+        <v>213</v>
+      </c>
+      <c r="D61" s="20">
+        <v>21.150000000000002</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="F61" s="19">
-        <v>3</v>
-      </c>
-      <c r="G61" s="9"/>
+        <v>137</v>
+      </c>
+      <c r="F61" s="21">
+        <v>2</v>
+      </c>
+      <c r="G61" s="19"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="10" t="s">
         <v>225</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="D62" s="18">
-        <v>20.059999999999999</v>
+        <v>214</v>
+      </c>
+      <c r="D62" s="20">
+        <v>21.55</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="F62" s="19">
-        <v>2</v>
-      </c>
-      <c r="G62" s="9"/>
+        <v>138</v>
+      </c>
+      <c r="F62" s="21">
+        <v>3</v>
+      </c>
+      <c r="G62" s="19"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="10" t="s">
         <v>225</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="D63" s="18">
-        <v>35.58</v>
+        <v>215</v>
+      </c>
+      <c r="D63" s="20">
+        <v>20.059999999999999</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F63" s="19">
-        <v>4</v>
-      </c>
-      <c r="G63" s="9"/>
+        <v>139</v>
+      </c>
+      <c r="F63" s="21">
+        <v>2</v>
+      </c>
+      <c r="G63" s="19"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="D64" s="18">
-        <v>11.91</v>
+        <v>216</v>
+      </c>
+      <c r="D64" s="20">
+        <v>35.58</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="F64" s="19">
-        <v>0</v>
-      </c>
-      <c r="G64" s="9"/>
+        <v>140</v>
+      </c>
+      <c r="F64" s="21">
+        <v>4</v>
+      </c>
+      <c r="G64" s="19"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="10" t="s">
         <v>226</v>
       </c>
       <c r="B65" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D65" s="20">
+        <v>12.75</v>
+      </c>
+      <c r="E65" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="F65" s="21">
+        <v>3</v>
+      </c>
+      <c r="G65" s="19"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B66" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C65" s="12" t="s">
+      <c r="C66" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="D65" s="18">
+      <c r="D66" s="20">
         <v>31.25</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E66" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="F65" s="19">
+      <c r="F66" s="21">
         <v>2</v>
       </c>
-      <c r="G65" s="9"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="13" t="s">
+      <c r="G66" s="19"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B67" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C66" s="15" t="s">
+      <c r="C67" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="D66" s="16">
-        <v>31.25</v>
-      </c>
-      <c r="E66" s="14" t="s">
+      <c r="D67" s="16">
+        <v>32.82</v>
+      </c>
+      <c r="E67" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="F66" s="17">
-        <v>0</v>
-      </c>
-      <c r="G66" s="9"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D67" s="20">
-        <v>29.48</v>
-      </c>
-      <c r="E67" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="F67" s="21">
-        <v>1</v>
-      </c>
-      <c r="G67" s="9"/>
+      <c r="F67" s="17">
+        <v>3</v>
+      </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>224</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D68" s="20">
-        <v>32</v>
+        <v>157</v>
+      </c>
+      <c r="D68" s="22">
+        <v>29.48</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="F68" s="21">
-        <v>2</v>
+        <v>144</v>
+      </c>
+      <c r="F68" s="23">
+        <v>1</v>
       </c>
       <c r="G68" s="9"/>
     </row>
@@ -2625,19 +2637,19 @@
         <v>224</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D69" s="20">
+        <v>158</v>
+      </c>
+      <c r="D69" s="22">
         <v>32</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="F69" s="21">
-        <v>3</v>
+        <v>145</v>
+      </c>
+      <c r="F69" s="23">
+        <v>2</v>
       </c>
       <c r="G69" s="9"/>
     </row>
@@ -2646,18 +2658,18 @@
         <v>224</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="D70" s="20">
-        <v>32.65</v>
+        <v>159</v>
+      </c>
+      <c r="D70" s="22">
+        <v>32</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F70" s="21">
+        <v>146</v>
+      </c>
+      <c r="F70" s="23">
         <v>3</v>
       </c>
       <c r="G70" s="9"/>
@@ -2667,19 +2679,19 @@
         <v>224</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D71" s="20">
-        <v>114.9</v>
+        <v>160</v>
+      </c>
+      <c r="D71" s="22">
+        <v>32.65</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="F71" s="21">
-        <v>1</v>
+        <v>147</v>
+      </c>
+      <c r="F71" s="23">
+        <v>2</v>
       </c>
       <c r="G71" s="9"/>
     </row>
@@ -2688,19 +2700,19 @@
         <v>224</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D72" s="20">
+        <v>161</v>
+      </c>
+      <c r="D72" s="22">
         <v>114.9</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="F72" s="21">
-        <v>2</v>
+        <v>148</v>
+      </c>
+      <c r="F72" s="23">
+        <v>1</v>
       </c>
       <c r="G72" s="9"/>
     </row>
@@ -2709,19 +2721,19 @@
         <v>224</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D73" s="20">
+        <v>162</v>
+      </c>
+      <c r="D73" s="22">
         <v>114.9</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="F73" s="21">
-        <v>1</v>
+        <v>149</v>
+      </c>
+      <c r="F73" s="23">
+        <v>2</v>
       </c>
       <c r="G73" s="9"/>
     </row>
@@ -2730,29 +2742,42 @@
         <v>224</v>
       </c>
       <c r="B74" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D74" s="22">
+        <v>114.9</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="F74" s="23">
+        <v>1</v>
+      </c>
+      <c r="G74" s="9"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B75" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D74" s="20">
+      <c r="D75" s="22">
         <v>113.10000000000001</v>
       </c>
-      <c r="E74" s="9" t="s">
+      <c r="E75" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="F74" s="21">
+      <c r="F75" s="23">
         <v>2</v>
       </c>
-      <c r="G74" s="9"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
+      <c r="G75" s="9"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
@@ -5683,13 +5708,21 @@
       <c r="F441" s="5"/>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A442" s="2"/>
+      <c r="A442" s="5"/>
+      <c r="B442" s="5"/>
+      <c r="C442" s="5"/>
+      <c r="D442" s="5"/>
+      <c r="E442" s="5"/>
+      <c r="F442" s="5"/>
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A443" s="2"/>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A444" s="2"/>
+    </row>
+    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A445" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
